--- a/功能清单.xlsx
+++ b/功能清单.xlsx
@@ -86,7 +86,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -152,11 +152,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -190,6 +204,17 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -604,11 +629,11 @@
           <t>移动端 · 故事</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="16" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -808,11 +833,11 @@
           <t>移动端 · 互动</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="16" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -980,11 +1005,11 @@
           <t>移动端 · 话题</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="16" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1088,11 +1113,11 @@
           <t>移动端 · 用户</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="16" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1292,11 +1317,11 @@
           <t>管理后台</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="14" t="n"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="14" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="16" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1421,6 +1446,102 @@
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>已上线</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>管理-05</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>精选故事</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>人工筛选优质故事设为精选，展示在精选列表</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>已上线</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>管理-06</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>敏感词管理</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>维护敏感词库，命中词自动过滤，支持热加载缓存</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>已上线</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>管理-07</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>管理后台</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>列表查看全部用户，停用账号/恢复，重置登录密码</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>管理端</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
